--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/THBG_0726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/THBG_0726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D30AA5E-F071-45E5-9C8E-DCA9D9C8E264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797EC9CE-A220-4DCA-91D4-8A8F65FA5A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="BG" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$K$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$K$30</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="59">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -49,9 +49,6 @@
     <t>Website: http://vnetgps.vn/</t>
   </si>
   <si>
-    <t>TBP. Bảo Hành</t>
-  </si>
-  <si>
     <t>Người Lập</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
   </si>
   <si>
     <t>Xác Định Lỗi</t>
-  </si>
-  <si>
-    <t>Tổng</t>
   </si>
   <si>
     <t>Mô Tả Linh 
@@ -86,9 +80,6 @@
     <t>Model</t>
   </si>
   <si>
-    <t>TỔNG HỢP PHÍ DỊCH VỤ SỬA CHỮA THÁNG 7</t>
-  </si>
-  <si>
     <t>Hà Nội, ngày 28 tháng 07 năm 2026</t>
   </si>
   <si>
@@ -131,9 +122,6 @@
     <t>Module SIM EC25</t>
   </si>
   <si>
-    <t>Công nợ ghi KD Lực</t>
-  </si>
-  <si>
     <t>00BD000714</t>
   </si>
   <si>
@@ -147,6 +135,75 @@
   </si>
   <si>
     <t>Đại lý Anh Tuấn Bắc Giang</t>
+  </si>
+  <si>
+    <t>Đại lý Anh Tuấn Ninh Bình</t>
+  </si>
+  <si>
+    <t>VNSH02</t>
+  </si>
+  <si>
+    <t>0032003E43</t>
+  </si>
+  <si>
+    <t>00BD000BFC</t>
+  </si>
+  <si>
+    <t>Thường xuyên mất GPS</t>
+  </si>
+  <si>
+    <t>Module GPS</t>
+  </si>
+  <si>
+    <t>MOSFET</t>
+  </si>
+  <si>
+    <t>00BD000C72</t>
+  </si>
+  <si>
+    <t>00320091D3</t>
+  </si>
+  <si>
+    <t>Khách lẻ</t>
+  </si>
+  <si>
+    <t>00320026F0</t>
+  </si>
+  <si>
+    <t>Module SIM EC20</t>
+  </si>
+  <si>
+    <t>Đại lý AT. 
+Việt Nam</t>
+  </si>
+  <si>
+    <t>TP. Kỹ Thuật</t>
+  </si>
+  <si>
+    <t>Đào Văn Thông</t>
+  </si>
+  <si>
+    <t>TP. KTTH</t>
+  </si>
+  <si>
+    <t>Trần Thị Thu Hà</t>
+  </si>
+  <si>
+    <t>Giám Đốc</t>
+  </si>
+  <si>
+    <t>Nguyễn Hải</t>
+  </si>
+  <si>
+    <t>TỔNG HỢP PHÍ DỊCH VỤ SỬA CHỮA BẢO HÀNH THÁNG 7/2026</t>
+  </si>
+  <si>
+    <t>Công nợ ghi 
+kinh doanh Lực</t>
+  </si>
+  <si>
+    <t>Đã thanh toán 
+tiền mặt cho kế toán 08/07/2026</t>
   </si>
 </sst>
 </file>
@@ -265,7 +322,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -431,11 +488,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -472,9 +540,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="10"/>
     </xf>
@@ -493,9 +558,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="13"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -520,10 +582,88 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -541,101 +681,20 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -999,7 +1058,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB43"/>
+  <dimension ref="A1:AB49"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
@@ -1012,7 +1071,7 @@
     <col min="8" max="8" width="11.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" style="3" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="12.140625" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="12.5703125" style="29" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="27" customWidth="1"/>
     <col min="12" max="13" width="9.140625" style="1"/>
     <col min="14" max="15" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="26" width="9.140625" style="1"/>
@@ -1022,496 +1081,683 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="68"/>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="37" t="s">
+      <c r="A1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="39"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="46"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="40" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="42"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="43" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="55"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="45"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="46" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="48"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="55"/>
     </row>
     <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="34"/>
+      <c r="A5" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
+      <c r="A6" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="15"/>
+      <c r="H6" s="14"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
-      <c r="K6" s="58" t="s">
-        <v>21</v>
+      <c r="K6" s="30" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
+      <c r="A7" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="15"/>
+      <c r="H7" s="14"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="59"/>
+      <c r="K7" s="31"/>
     </row>
     <row r="8" spans="1:28" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="26" t="s">
+      <c r="C8" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB8" s="2"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="23">
+        <v>1</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB8" s="2"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="25">
+      <c r="C9" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="20">
         <v>1</v>
       </c>
-      <c r="B9" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="22">
-        <v>1</v>
-      </c>
-      <c r="J9" s="24">
+      <c r="J9" s="22">
         <v>200000</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="22">
         <f>SUM(I9*J9)</f>
         <v>200000</v>
       </c>
       <c r="AB9" s="2"/>
     </row>
-    <row r="10" spans="1:28" ht="36" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
+    <row r="10" spans="1:28" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="23">
         <v>2</v>
       </c>
-      <c r="B10" s="65"/>
-      <c r="C10" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="22">
+      <c r="B10" s="37"/>
+      <c r="C10" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="63"/>
+      <c r="F10" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="20">
         <v>1</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="22">
         <v>750000</v>
       </c>
-      <c r="K10" s="24">
+      <c r="K10" s="22">
         <f>SUM(I10*J10)</f>
         <v>750000</v>
       </c>
       <c r="AB10" s="2"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="25">
+      <c r="A11" s="23">
         <v>3</v>
       </c>
-      <c r="B11" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="25" t="s">
+      <c r="B11" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="22">
+      <c r="E11" s="63"/>
+      <c r="F11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="20">
         <v>1</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="22">
         <v>150000</v>
       </c>
-      <c r="K11" s="24">
-        <f t="shared" ref="K10:K12" si="0">SUM(I11*J11)</f>
+      <c r="K11" s="22">
+        <f t="shared" ref="K11:K12" si="0">SUM(I11*J11)</f>
         <v>150000</v>
       </c>
       <c r="AB11" s="2"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="25">
+      <c r="A12" s="23">
         <v>4</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="22">
+      <c r="B12" s="39"/>
+      <c r="C12" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="63"/>
+      <c r="F12" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="20">
         <v>1</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="22">
         <v>150000</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="22">
         <f t="shared" si="0"/>
         <v>150000</v>
       </c>
       <c r="AB12" s="2"/>
     </row>
-    <row r="13" spans="1:28" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25">
+    <row r="13" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="23">
         <v>5</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="AB13" s="29"/>
+      <c r="B13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="63"/>
+      <c r="F13" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="20">
+        <v>1</v>
+      </c>
+      <c r="J13" s="22">
+        <v>260000</v>
+      </c>
+      <c r="K13" s="22">
+        <f>SUM(I13*J13)</f>
+        <v>260000</v>
+      </c>
+      <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="23">
+        <v>6</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="63"/>
+      <c r="F14" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="21">
-        <f>SUM(K9:K12)</f>
-        <v>1250000</v>
+      <c r="I14" s="20">
+        <v>1</v>
+      </c>
+      <c r="J14" s="22">
+        <v>150000</v>
+      </c>
+      <c r="K14" s="22">
+        <f t="shared" ref="K14:K18" si="1">SUM(I14*J14)</f>
+        <v>150000</v>
       </c>
       <c r="AB14" s="2"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="10"/>
+      <c r="A15" s="23">
+        <v>7</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="20">
+        <v>2</v>
+      </c>
+      <c r="J15" s="22">
+        <v>100000</v>
+      </c>
+      <c r="K15" s="22">
+        <f t="shared" si="1"/>
+        <v>200000</v>
+      </c>
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="58"/>
+      <c r="A16" s="23">
+        <v>8</v>
+      </c>
+      <c r="B16" s="61"/>
+      <c r="C16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="63"/>
+      <c r="F16" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="20">
+        <v>1</v>
+      </c>
+      <c r="J16" s="22">
+        <v>260000</v>
+      </c>
+      <c r="K16" s="22">
+        <f t="shared" si="1"/>
+        <v>260000</v>
+      </c>
       <c r="AB16" s="2"/>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="52" t="s">
+    <row r="17" spans="1:28" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="23">
+        <v>9</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="63"/>
+      <c r="F17" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="20">
+        <v>1</v>
+      </c>
+      <c r="J17" s="22">
+        <v>150000</v>
+      </c>
+      <c r="K17" s="22">
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+      <c r="AB17" s="2"/>
+    </row>
+    <row r="18" spans="1:28" ht="36" x14ac:dyDescent="0.25">
+      <c r="A18" s="23">
+        <v>10</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="20">
+        <v>1</v>
+      </c>
+      <c r="J18" s="22">
+        <v>600000</v>
+      </c>
+      <c r="K18" s="22">
+        <f t="shared" si="1"/>
+        <v>600000</v>
+      </c>
+      <c r="AB18" s="2"/>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" s="23"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="AB19" s="2"/>
+    </row>
+    <row r="20" spans="1:28" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="AB20" s="27"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="10"/>
+      <c r="AB21" s="2"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="30"/>
+      <c r="AB22" s="2"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="AB17" s="2"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="AB23" s="2"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="53" t="s">
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="AB18" s="2"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="61"/>
-      <c r="AB19" s="2"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7" t="s">
+      <c r="E24" s="41"/>
+      <c r="F24" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="AB24" s="2"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="33"/>
+      <c r="AB25" s="2"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="62"/>
-      <c r="AB20" s="2"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="62"/>
-      <c r="AB21" s="2"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="62"/>
-      <c r="AB22" s="2"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="54" t="s">
+      <c r="H26" s="15"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="34"/>
+      <c r="AB26" s="2"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="34"/>
+      <c r="AB27" s="2"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="34"/>
+      <c r="AB28" s="2"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="11"/>
-      <c r="AB23" s="2"/>
-    </row>
-    <row r="24" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="63"/>
-      <c r="AB24" s="2"/>
-    </row>
-    <row r="25" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="G25" s="4"/>
-      <c r="AB25" s="2"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="AB26" s="2"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="AB27" s="2"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="AB28" s="2"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="11"/>
       <c r="AB29" s="2"/>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="35"/>
       <c r="AB30" s="2"/>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="G31" s="4"/>
       <c r="AB31" s="2"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
@@ -1550,18 +1796,35 @@
     <row r="43" spans="28:28" x14ac:dyDescent="0.25">
       <c r="AB43" s="2"/>
     </row>
+    <row r="44" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB44" s="2"/>
+    </row>
+    <row r="45" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB45" s="2"/>
+    </row>
+    <row r="46" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB46" s="2"/>
+    </row>
+    <row r="47" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB47" s="2"/>
+    </row>
+    <row r="48" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB48" s="2"/>
+    </row>
+    <row r="49" spans="28:28" x14ac:dyDescent="0.25">
+      <c r="AB49" s="2"/>
+    </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="17">
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A23:E23"/>
+  <mergeCells count="27">
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H29:K29"/>
     <mergeCell ref="A1:D4"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="E2:K2"/>
@@ -1570,6 +1833,17 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="E9:E17"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/THBG_0726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/THBG_0726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797EC9CE-A220-4DCA-91D4-8A8F65FA5A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D7B402-FC78-4383-BCDF-7DF8D5EECB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BG" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$K$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$K$28</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
@@ -80,9 +80,6 @@
     <t>Model</t>
   </si>
   <si>
-    <t>Hà Nội, ngày 28 tháng 07 năm 2026</t>
-  </si>
-  <si>
     <t>Khách Hàng</t>
   </si>
   <si>
@@ -204,6 +201,9 @@
   <si>
     <t>Đã thanh toán 
 tiền mặt cho kế toán 08/07/2026</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày 29 tháng 07 năm 2026</t>
   </si>
 </sst>
 </file>
@@ -503,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -537,9 +537,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="10"/>
     </xf>
@@ -606,24 +603,24 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -681,20 +678,14 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1058,7 +1049,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB49"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
@@ -1071,7 +1062,7 @@
     <col min="8" max="8" width="11.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" style="3" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="12.140625" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="12.5703125" style="27" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="26" customWidth="1"/>
     <col min="12" max="13" width="9.140625" style="1"/>
     <col min="14" max="15" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="26" width="9.140625" style="1"/>
@@ -1081,683 +1072,661 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="43"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="44" t="s">
+      <c r="A1" s="42"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="46"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="45"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="47" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="50" t="s">
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="53" t="s">
+      <c r="A4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="55"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="54"/>
     </row>
     <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="58"/>
+      <c r="A5" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
+      <c r="A6" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="14"/>
+      <c r="H6" s="13"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
-      <c r="K6" s="30" t="s">
-        <v>18</v>
+      <c r="K6" s="29" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
+      <c r="A7" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="14"/>
+      <c r="H7" s="13"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="31"/>
+      <c r="K7" s="30"/>
     </row>
     <row r="8" spans="1:28" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="24" t="s">
+      <c r="E8" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="32" t="s">
+      <c r="K8" s="31" t="s">
         <v>12</v>
       </c>
       <c r="AB8" s="2"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="23">
+      <c r="A9" s="22">
         <v>1</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="D9" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="E9" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="23" t="s">
+      <c r="G9" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="19">
         <v>1</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="21">
         <v>200000</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="21">
         <f>SUM(I9*J9)</f>
         <v>200000</v>
       </c>
       <c r="AB9" s="2"/>
     </row>
     <row r="10" spans="1:28" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="23">
+      <c r="A10" s="22">
         <v>2</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="61"/>
+      <c r="C10" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="63"/>
-      <c r="F10" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="19">
         <v>1</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="21">
         <v>750000</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="21">
         <f>SUM(I10*J10)</f>
         <v>750000</v>
       </c>
       <c r="AB10" s="2"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="23">
+      <c r="A11" s="22">
         <v>3</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="63"/>
-      <c r="F11" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="62"/>
+      <c r="F11" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="19">
         <v>1</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11" s="21">
         <v>150000</v>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="21">
         <f t="shared" ref="K11:K12" si="0">SUM(I11*J11)</f>
         <v>150000</v>
       </c>
       <c r="AB11" s="2"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="23">
+      <c r="A12" s="22">
         <v>4</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="23" t="s">
+      <c r="B12" s="40"/>
+      <c r="C12" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="62"/>
+      <c r="F12" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="63"/>
-      <c r="F12" s="26" t="s">
+      <c r="G12" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="19">
         <v>1</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12" s="21">
         <v>150000</v>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="21">
         <f t="shared" si="0"/>
         <v>150000</v>
       </c>
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23">
+      <c r="A13" s="22">
         <v>5</v>
       </c>
       <c r="B13" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="D13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="63"/>
-      <c r="F13" s="21" t="s">
+      <c r="E13" s="62"/>
+      <c r="F13" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="19">
         <v>1</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="21">
         <v>260000</v>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="21">
         <f>SUM(I13*J13)</f>
         <v>260000</v>
       </c>
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+      <c r="A14" s="22">
         <v>6</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="63"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="62"/>
       <c r="F14" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="19">
         <v>1</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="21">
         <v>150000</v>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="21">
         <f t="shared" ref="K14:K18" si="1">SUM(I14*J14)</f>
         <v>150000</v>
       </c>
       <c r="AB14" s="2"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="23">
+      <c r="A15" s="22">
         <v>7</v>
       </c>
       <c r="B15" s="39"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="20" t="s">
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="19">
         <v>2</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="21">
         <v>100000</v>
       </c>
-      <c r="K15" s="22">
+      <c r="K15" s="21">
         <f t="shared" si="1"/>
         <v>200000</v>
       </c>
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="23">
+      <c r="A16" s="22">
         <v>8</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="62" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="63"/>
-      <c r="F16" s="21" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="62"/>
+      <c r="F16" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="19">
         <v>1</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16" s="21">
         <v>260000</v>
       </c>
-      <c r="K16" s="22">
+      <c r="K16" s="21">
         <f t="shared" si="1"/>
         <v>260000</v>
       </c>
       <c r="AB16" s="2"/>
     </row>
     <row r="17" spans="1:28" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="23">
+      <c r="A17" s="22">
         <v>9</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="63"/>
-      <c r="F17" s="26" t="s">
+      <c r="B17" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="62"/>
+      <c r="F17" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="19">
         <v>1</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="21">
         <v>150000</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="21">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
       <c r="AB17" s="2"/>
     </row>
     <row r="18" spans="1:28" ht="36" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
+      <c r="A18" s="19">
         <v>10</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="23" t="s">
+      <c r="E18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="19">
         <v>1</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18" s="21">
         <v>600000</v>
       </c>
-      <c r="K18" s="22">
+      <c r="K18" s="21">
         <f t="shared" si="1"/>
         <v>600000</v>
       </c>
       <c r="AB18" s="2"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="23"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="10"/>
       <c r="AB19" s="2"/>
     </row>
-    <row r="20" spans="1:28" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="AB20" s="27"/>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="29"/>
+      <c r="AB20" s="2"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="10"/>
+      <c r="A21" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
       <c r="AB21" s="2"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="30"/>
+      <c r="A22" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
       <c r="AB22" s="2"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="32"/>
       <c r="AB23" s="2"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="33"/>
       <c r="AB24" s="2"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
       <c r="K25" s="33"/>
       <c r="AB25" s="2"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="15"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="14"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
-      <c r="K26" s="34"/>
+      <c r="K26" s="33"/>
       <c r="AB26" s="2"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="34"/>
+      <c r="A27" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="11"/>
       <c r="AB27" s="2"/>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
+    <row r="28" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
       <c r="K28" s="34"/>
       <c r="AB28" s="2"/>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="11"/>
+    <row r="29" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="G29" s="4"/>
       <c r="AB29" s="2"/>
     </row>
-    <row r="30" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="35"/>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB30" s="2"/>
     </row>
-    <row r="31" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="G31" s="4"/>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="AB31" s="2"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
@@ -1807,29 +1776,10 @@
     </row>
     <row r="47" spans="28:28" x14ac:dyDescent="0.25">
       <c r="AB47" s="2"/>
-    </row>
-    <row r="48" spans="28:28" x14ac:dyDescent="0.25">
-      <c r="AB48" s="2"/>
-    </row>
-    <row r="49" spans="28:28" x14ac:dyDescent="0.25">
-      <c r="AB49" s="2"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="27">
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="E3:K3"/>
-    <mergeCell ref="E4:K4"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A6:D6"/>
@@ -1839,11 +1789,24 @@
     <mergeCell ref="E9:E17"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="E3:K3"/>
+    <mergeCell ref="E4:K4"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/THBG_0726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/THBG_0726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D7B402-FC78-4383-BCDF-7DF8D5EECB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AD6198-BC10-4495-AE6A-35C706E44D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>Hà Nội, ngày 29 tháng 07 năm 2026</t>
+  </si>
+  <si>
+    <t>ID này khách chưa phản hồi lại báo giá</t>
   </si>
 </sst>
 </file>
@@ -213,7 +216,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,6 +310,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -503,7 +512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -606,87 +615,88 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1072,87 +1082,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43" t="s">
+      <c r="A1" s="46"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="45"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="49"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="46" t="s">
+      <c r="A2" s="46"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="48"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="52"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="49" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="51"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="55"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="52" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="54"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="57"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="38"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -1164,11 +1174,11 @@
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -1218,7 +1228,7 @@
       <c r="A9" s="22">
         <v>1</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="41" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -1227,7 +1237,7 @@
       <c r="D9" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="43" t="s">
         <v>56</v>
       </c>
       <c r="F9" s="22" t="s">
@@ -1249,20 +1259,23 @@
         <f>SUM(I9*J9)</f>
         <v>200000</v>
       </c>
+      <c r="L9" s="63" t="s">
+        <v>59</v>
+      </c>
       <c r="AB9" s="2"/>
     </row>
     <row r="10" spans="1:28" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <v>2</v>
       </c>
-      <c r="B10" s="61"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="22" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="62"/>
+      <c r="E10" s="45"/>
       <c r="F10" s="25" t="s">
         <v>16</v>
       </c>
@@ -1288,7 +1301,7 @@
       <c r="A11" s="22">
         <v>3</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="43" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="22" t="s">
@@ -1297,7 +1310,7 @@
       <c r="D11" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="62"/>
+      <c r="E11" s="45"/>
       <c r="F11" s="25" t="s">
         <v>33</v>
       </c>
@@ -1323,14 +1336,14 @@
       <c r="A12" s="22">
         <v>4</v>
       </c>
-      <c r="B12" s="40"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="22" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="62"/>
+      <c r="E12" s="45"/>
       <c r="F12" s="25" t="s">
         <v>33</v>
       </c>
@@ -1356,7 +1369,7 @@
       <c r="A13" s="22">
         <v>5</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="43" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="19" t="s">
@@ -1365,7 +1378,7 @@
       <c r="D13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="62"/>
+      <c r="E13" s="45"/>
       <c r="F13" s="20" t="s">
         <v>40</v>
       </c>
@@ -1391,15 +1404,15 @@
       <c r="A14" s="22">
         <v>6</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="60" t="s">
+      <c r="B14" s="61"/>
+      <c r="C14" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="60" t="s">
+      <c r="D14" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="62"/>
-      <c r="F14" s="38" t="s">
+      <c r="E14" s="45"/>
+      <c r="F14" s="43" t="s">
         <v>33</v>
       </c>
       <c r="G14" s="20" t="s">
@@ -1424,11 +1437,11 @@
       <c r="A15" s="22">
         <v>7</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="40"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="19" t="s">
         <v>42</v>
       </c>
@@ -1451,14 +1464,14 @@
       <c r="A16" s="22">
         <v>8</v>
       </c>
-      <c r="B16" s="40"/>
+      <c r="B16" s="44"/>
       <c r="C16" s="19" t="s">
         <v>37</v>
       </c>
       <c r="D16" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="62"/>
+      <c r="E16" s="45"/>
       <c r="F16" s="20" t="s">
         <v>40</v>
       </c>
@@ -1493,7 +1506,7 @@
       <c r="D17" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="62"/>
+      <c r="E17" s="45"/>
       <c r="F17" s="25" t="s">
         <v>33</v>
       </c>
@@ -1581,47 +1594,47 @@
       <c r="AB20" s="2"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37" t="s">
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37" t="s">
+      <c r="E21" s="60"/>
+      <c r="F21" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37" t="s">
+      <c r="G21" s="60"/>
+      <c r="H21" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
       <c r="AB21" s="2"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36" t="s">
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36" t="s">
+      <c r="E22" s="59"/>
+      <c r="F22" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36" t="s">
+      <c r="G22" s="59"/>
+      <c r="H22" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
       <c r="AB22" s="2"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
@@ -1683,25 +1696,25 @@
       <c r="AB26" s="2"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41" t="s">
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41" t="s">
+      <c r="E27" s="62"/>
+      <c r="F27" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41" t="s">
+      <c r="G27" s="62"/>
+      <c r="H27" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
       <c r="L27" s="11"/>
       <c r="AB27" s="2"/>
     </row>
@@ -1780,20 +1793,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="27">
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="E9:E17"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="E3:K3"/>
-    <mergeCell ref="E4:K4"/>
     <mergeCell ref="H22:K22"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="F22:G22"/>
@@ -1807,6 +1806,20 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="E3:K3"/>
+    <mergeCell ref="E4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="E9:E17"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
